--- a/docs/templates/mock_drive/2026001 — Rockland/SOW/2026001_SOW_v1.xlsx
+++ b/docs/templates/mock_drive/2026001 — Rockland/SOW/2026001_SOW_v1.xlsx
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
